--- a/data/gravel/BMC URS 01 2025.xlsx
+++ b/data/gravel/BMC URS 01 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel copy/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16F63088-9E74-B241-88DF-C372CB86EE9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{031D0EFD-5F18-D24F-87DF-67D63E2CAFBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="13120" windowHeight="6100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="20620" windowHeight="15320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="125">
   <si>
     <t>brand</t>
   </si>
@@ -35,9 +35,6 @@
   </si>
   <si>
     <t>model year</t>
-  </si>
-  <si>
-    <t>2024</t>
   </si>
   <si>
     <t>input date</t>
@@ -755,63 +752,63 @@
       <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" t="s">
-        <v>5</v>
+      <c r="B3">
+        <v>2025</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" t="s">
         <v>7</v>
-      </c>
-      <c r="B5" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" t="s">
         <v>10</v>
-      </c>
-      <c r="B7" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" t="s">
         <v>12</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>13</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>14</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>15</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>16</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>17</v>
-      </c>
-      <c r="G8" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" t="s">
         <v>19</v>
-      </c>
-      <c r="B9" t="s">
-        <v>20</v>
       </c>
       <c r="C9">
         <v>390</v>
@@ -831,10 +828,10 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" t="s">
         <v>21</v>
-      </c>
-      <c r="B10" t="s">
-        <v>22</v>
       </c>
       <c r="C10">
         <v>560</v>
@@ -854,10 +851,10 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" t="s">
         <v>23</v>
-      </c>
-      <c r="B11" t="s">
-        <v>24</v>
       </c>
       <c r="C11">
         <v>120</v>
@@ -877,10 +874,10 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" t="s">
         <v>25</v>
-      </c>
-      <c r="B12" t="s">
-        <v>26</v>
       </c>
       <c r="C12">
         <v>80</v>
@@ -900,10 +897,10 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" t="s">
         <v>27</v>
-      </c>
-      <c r="B13" t="s">
-        <v>28</v>
       </c>
       <c r="C13">
         <v>76</v>
@@ -923,10 +920,10 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" t="s">
         <v>29</v>
-      </c>
-      <c r="B14" t="s">
-        <v>30</v>
       </c>
       <c r="C14">
         <v>170</v>
@@ -946,10 +943,10 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15" t="s">
         <v>31</v>
-      </c>
-      <c r="B15" t="s">
-        <v>32</v>
       </c>
       <c r="C15">
         <v>405</v>
@@ -969,10 +966,10 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
+        <v>32</v>
+      </c>
+      <c r="B16" t="s">
         <v>33</v>
-      </c>
-      <c r="B16" t="s">
-        <v>34</v>
       </c>
       <c r="C16">
         <v>50</v>
@@ -992,10 +989,10 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
+        <v>34</v>
+      </c>
+      <c r="B17" t="s">
         <v>35</v>
-      </c>
-      <c r="B17" t="s">
-        <v>36</v>
       </c>
       <c r="C17">
         <v>633</v>
@@ -1015,10 +1012,10 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
+        <v>36</v>
+      </c>
+      <c r="B18" t="s">
         <v>37</v>
-      </c>
-      <c r="B18" t="s">
-        <v>38</v>
       </c>
       <c r="C18">
         <v>133</v>
@@ -1038,10 +1035,10 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
+        <v>38</v>
+      </c>
+      <c r="B19" t="s">
         <v>39</v>
-      </c>
-      <c r="B19" t="s">
-        <v>40</v>
       </c>
       <c r="C19">
         <v>69</v>
@@ -1061,10 +1058,10 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" t="s">
         <v>41</v>
-      </c>
-      <c r="B20" t="s">
-        <v>42</v>
       </c>
       <c r="C20">
         <v>430</v>
@@ -1084,10 +1081,10 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
+        <v>42</v>
+      </c>
+      <c r="B21" t="s">
         <v>43</v>
-      </c>
-      <c r="B21" t="s">
-        <v>44</v>
       </c>
       <c r="C21">
         <v>74.5</v>
@@ -1107,10 +1104,10 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
+        <v>44</v>
+      </c>
+      <c r="B22" t="s">
         <v>45</v>
-      </c>
-      <c r="B22" t="s">
-        <v>46</v>
       </c>
       <c r="C22">
         <v>430</v>
@@ -1130,10 +1127,10 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
+        <v>46</v>
+      </c>
+      <c r="B23" t="s">
         <v>47</v>
-      </c>
-      <c r="B23" t="s">
-        <v>48</v>
       </c>
       <c r="C23">
         <v>310</v>
@@ -1153,10 +1150,10 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
+        <v>48</v>
+      </c>
+      <c r="B24" t="s">
         <v>49</v>
-      </c>
-      <c r="B24" t="s">
-        <v>50</v>
       </c>
       <c r="C24">
         <v>0</v>
@@ -1176,10 +1173,10 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
+        <v>50</v>
+      </c>
+      <c r="B25" t="s">
         <v>51</v>
-      </c>
-      <c r="B25" t="s">
-        <v>52</v>
       </c>
       <c r="C25">
         <v>727</v>
@@ -1199,10 +1196,10 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
+        <v>52</v>
+      </c>
+      <c r="B26" t="s">
         <v>53</v>
-      </c>
-      <c r="B26" t="s">
-        <v>54</v>
       </c>
       <c r="C26">
         <v>420</v>
@@ -1222,10 +1219,10 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
+        <v>54</v>
+      </c>
+      <c r="B27" t="s">
         <v>55</v>
-      </c>
-      <c r="B27" t="s">
-        <v>56</v>
       </c>
       <c r="C27">
         <v>0</v>
@@ -1245,10 +1242,10 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
+        <v>56</v>
+      </c>
+      <c r="B28" t="s">
         <v>57</v>
-      </c>
-      <c r="B28" t="s">
-        <v>58</v>
       </c>
       <c r="C28">
         <v>72</v>
@@ -1268,10 +1265,10 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
+        <v>58</v>
+      </c>
+      <c r="B29" t="s">
         <v>59</v>
-      </c>
-      <c r="B29" t="s">
-        <v>60</v>
       </c>
       <c r="C29">
         <v>545</v>
@@ -1291,10 +1288,10 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
+        <v>60</v>
+      </c>
+      <c r="B30" t="s">
         <v>61</v>
-      </c>
-      <c r="B30" t="s">
-        <v>62</v>
       </c>
       <c r="C30">
         <v>84</v>
@@ -1314,10 +1311,10 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
+        <v>62</v>
+      </c>
+      <c r="B31" t="s">
         <v>63</v>
-      </c>
-      <c r="B31" t="s">
-        <v>64</v>
       </c>
       <c r="C31">
         <v>1052</v>
@@ -1337,12 +1334,12 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C33">
         <v>700</v>
@@ -1362,7 +1359,7 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C34">
         <v>44</v>
@@ -1382,7 +1379,7 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C35">
         <v>47</v>
@@ -1402,7 +1399,7 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C36">
         <v>160</v>
@@ -1422,7 +1419,7 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C37">
         <v>166</v>
@@ -1442,272 +1439,266 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
+        <v>70</v>
+      </c>
+      <c r="B39" t="s">
         <v>71</v>
-      </c>
-      <c r="B39" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
+        <v>119</v>
+      </c>
+      <c r="B40" t="s">
         <v>120</v>
-      </c>
-      <c r="B40" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
+        <v>121</v>
+      </c>
+      <c r="B41" t="s">
         <v>122</v>
-      </c>
-      <c r="B41" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
+        <v>123</v>
+      </c>
+      <c r="B42" t="s">
         <v>124</v>
-      </c>
-      <c r="B42" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
+        <v>72</v>
+      </c>
+      <c r="B43" t="s">
         <v>73</v>
-      </c>
-      <c r="B43" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
+        <v>74</v>
+      </c>
+      <c r="B44" t="s">
         <v>75</v>
-      </c>
-      <c r="B44" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
+        <v>76</v>
+      </c>
+      <c r="B45" t="s">
         <v>77</v>
-      </c>
-      <c r="B45" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
+        <v>78</v>
+      </c>
+      <c r="B46" t="s">
         <v>79</v>
-      </c>
-      <c r="B46" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>83</v>
-      </c>
-      <c r="B49" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>85</v>
-      </c>
-      <c r="B50" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>86</v>
-      </c>
-      <c r="B51" t="s">
-        <v>76</v>
+        <v>85</v>
+      </c>
+      <c r="B51">
+        <v>10</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
+        <v>88</v>
+      </c>
+      <c r="B54" t="s">
         <v>89</v>
-      </c>
-      <c r="B54" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B57" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
+        <v>95</v>
+      </c>
+      <c r="B60" t="s">
         <v>96</v>
-      </c>
-      <c r="B60" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
+        <v>98</v>
+      </c>
+      <c r="B62" t="s">
         <v>99</v>
-      </c>
-      <c r="B62" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B65" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B66" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
+        <v>104</v>
+      </c>
+      <c r="B67" t="s">
         <v>105</v>
-      </c>
-      <c r="B67" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
+        <v>106</v>
+      </c>
+      <c r="B68" t="s">
         <v>107</v>
-      </c>
-      <c r="B68" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B69" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B70" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B71" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B73" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
+        <v>114</v>
+      </c>
+      <c r="B75" t="s">
         <v>115</v>
-      </c>
-      <c r="B75" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
+        <v>117</v>
+      </c>
+      <c r="B77" t="s">
         <v>118</v>
-      </c>
-      <c r="B77" t="s">
-        <v>119</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/BMC URS 01 2025.xlsx
+++ b/data/gravel/BMC URS 01 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{031D0EFD-5F18-D24F-87DF-67D63E2CAFBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81470122-118D-C744-A8F2-63473003A30D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="20620" windowHeight="15320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="126">
   <si>
     <t>brand</t>
   </si>
@@ -395,6 +395,9 @@
   </si>
   <si>
     <t>rigid</t>
+  </si>
+  <si>
+    <t>https://us.bmc-switzerland.com/cdn/shop/files/bmc-2026-urs-01-one-gravel-bike-black-1.jpg?v=1758295670&amp;width=1080</t>
   </si>
 </sst>
 </file>
@@ -772,6 +775,11 @@
         <v>7</v>
       </c>
     </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>125</v>
+      </c>
+    </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>9</v>

--- a/data/gravel/BMC URS 01 2025.xlsx
+++ b/data/gravel/BMC URS 01 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81470122-118D-C744-A8F2-63473003A30D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE7943C2-B05B-6B41-9DF2-539EBFD8B08E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="20620" windowHeight="15320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="128">
   <si>
     <t>brand</t>
   </si>
@@ -376,9 +376,6 @@
     <t>currency</t>
   </si>
   <si>
-    <t>us</t>
-  </si>
-  <si>
     <t>class</t>
   </si>
   <si>
@@ -398,17 +395,32 @@
   </si>
   <si>
     <t>https://us.bmc-switzerland.com/cdn/shop/files/bmc-2026-urs-01-one-gravel-bike-black-1.jpg?v=1758295670&amp;width=1080</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Grenchen, Switzerland</t>
+  </si>
+  <si>
+    <t>USD</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="14"/>
       <color rgb="FF000000"/>
       <name val="Futura"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Futura"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -431,8 +443,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -729,7 +742,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G77"/>
+  <dimension ref="A1:G78"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -777,7 +790,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
@@ -1455,26 +1468,26 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
+        <v>118</v>
+      </c>
+      <c r="B40" t="s">
         <v>119</v>
-      </c>
-      <c r="B40" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
+        <v>120</v>
+      </c>
+      <c r="B41" t="s">
         <v>121</v>
-      </c>
-      <c r="B41" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
+        <v>122</v>
+      </c>
+      <c r="B42" t="s">
         <v>123</v>
-      </c>
-      <c r="B42" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
@@ -1705,8 +1718,16 @@
       <c r="A77" t="s">
         <v>117</v>
       </c>
-      <c r="B77" t="s">
-        <v>118</v>
+      <c r="B77" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>125</v>
+      </c>
+      <c r="B78" t="s">
+        <v>126</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/BMC URS 01 2025.xlsx
+++ b/data/gravel/BMC URS 01 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE7943C2-B05B-6B41-9DF2-539EBFD8B08E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CBE02C3-1447-F047-974B-1553EFF5CB98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="20620" windowHeight="15320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11060" yWindow="2660" windowWidth="20620" windowHeight="15320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="129">
   <si>
     <t>brand</t>
   </si>
@@ -289,9 +289,6 @@
     <t>bottom_bracket</t>
   </si>
   <si>
-    <t>pf</t>
-  </si>
-  <si>
     <t>q_factor</t>
   </si>
   <si>
@@ -404,6 +401,12 @@
   </si>
   <si>
     <t>USD</t>
+  </si>
+  <si>
+    <t>press fit</t>
+  </si>
+  <si>
+    <t>internal</t>
   </si>
 </sst>
 </file>
@@ -790,7 +793,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
@@ -1468,26 +1471,26 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
+        <v>117</v>
+      </c>
+      <c r="B40" t="s">
         <v>118</v>
-      </c>
-      <c r="B40" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
+        <v>119</v>
+      </c>
+      <c r="B41" t="s">
         <v>120</v>
-      </c>
-      <c r="B41" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
+        <v>121</v>
+      </c>
+      <c r="B42" t="s">
         <v>122</v>
-      </c>
-      <c r="B42" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
@@ -1564,23 +1567,23 @@
       <c r="A54" t="s">
         <v>88</v>
       </c>
-      <c r="B54" t="s">
-        <v>89</v>
+      <c r="B54" s="1" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B57" t="s">
         <v>83</v>
@@ -1588,48 +1591,54 @@
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
+        <v>94</v>
+      </c>
+      <c r="B60" t="s">
         <v>95</v>
-      </c>
-      <c r="B60" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
+        <v>97</v>
+      </c>
+      <c r="B62" t="s">
         <v>98</v>
-      </c>
-      <c r="B62" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>100</v>
+        <v>99</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>101</v>
+        <v>100</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B65" t="s">
         <v>75</v>
@@ -1637,7 +1646,7 @@
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B66" t="s">
         <v>75</v>
@@ -1645,31 +1654,31 @@
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
+        <v>103</v>
+      </c>
+      <c r="B67" t="s">
         <v>104</v>
-      </c>
-      <c r="B67" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
+        <v>105</v>
+      </c>
+      <c r="B68" t="s">
         <v>106</v>
-      </c>
-      <c r="B68" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B69" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B70" t="s">
         <v>75</v>
@@ -1677,7 +1686,7 @@
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B71" t="s">
         <v>75</v>
@@ -1685,12 +1694,12 @@
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B73" t="s">
         <v>75</v>
@@ -1698,36 +1707,36 @@
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
+        <v>113</v>
+      </c>
+      <c r="B75" t="s">
         <v>114</v>
-      </c>
-      <c r="B75" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
+        <v>124</v>
+      </c>
+      <c r="B78" t="s">
         <v>125</v>
-      </c>
-      <c r="B78" t="s">
-        <v>126</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/BMC URS 01 2025.xlsx
+++ b/data/gravel/BMC URS 01 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CBE02C3-1447-F047-974B-1553EFF5CB98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6180F8D-195F-724A-B2C2-FB46E26308F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11060" yWindow="2660" windowWidth="20620" windowHeight="15320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8180" yWindow="2660" windowWidth="20620" windowHeight="15320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="135">
   <si>
     <t>brand</t>
   </si>
@@ -407,6 +407,24 @@
   </si>
   <si>
     <t>internal</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -745,7 +763,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G78"/>
+  <dimension ref="A1:G84"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1565,128 +1583,110 @@
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>88</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>89</v>
+        <v>130</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>90</v>
+        <v>131</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>91</v>
-      </c>
-      <c r="B57" t="s">
-        <v>83</v>
+        <v>132</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>92</v>
+        <v>133</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>93</v>
+        <v>134</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>94</v>
-      </c>
-      <c r="B60" t="s">
-        <v>95</v>
+        <v>88</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>97</v>
-      </c>
-      <c r="B62" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>99</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>128</v>
+        <v>91</v>
+      </c>
+      <c r="B63" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>100</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>128</v>
+        <v>92</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>101</v>
-      </c>
-      <c r="B65" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="B66" t="s">
-        <v>75</v>
+        <v>95</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>103</v>
-      </c>
-      <c r="B67" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="B68" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>107</v>
-      </c>
-      <c r="B69" t="s">
-        <v>106</v>
+        <v>99</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>108</v>
-      </c>
-      <c r="B70" t="s">
-        <v>75</v>
+        <v>100</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="B71" t="s">
         <v>75</v>
@@ -1694,48 +1694,96 @@
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>110</v>
+        <v>102</v>
+      </c>
+      <c r="B72" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="B73" t="s">
-        <v>75</v>
+        <v>104</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>112</v>
+        <v>105</v>
+      </c>
+      <c r="B74" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="B75" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>115</v>
+        <v>108</v>
+      </c>
+      <c r="B76" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>116</v>
-      </c>
-      <c r="B77" s="1" t="s">
-        <v>126</v>
+        <v>109</v>
+      </c>
+      <c r="B77" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>111</v>
+      </c>
+      <c r="B79" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>113</v>
+      </c>
+      <c r="B81" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>116</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
         <v>124</v>
       </c>
-      <c r="B78" t="s">
+      <c r="B84" t="s">
         <v>125</v>
       </c>
     </row>
